--- a/artfynd/A 58922-2024 artfynd.xlsx
+++ b/artfynd/A 58922-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1368,6 +1368,2250 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126518951</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80084</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>576556</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7256164</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126517759</v>
+      </c>
+      <c r="B9" t="n">
+        <v>75080</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577186</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7255953</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126516972</v>
+      </c>
+      <c r="B10" t="n">
+        <v>75067</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>308</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>577321</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7256133</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126517699</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91263</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>577229</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7255956</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126518234</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91245</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>576959</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7256037</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126515967</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>577501</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7256044</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126516771</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91241</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>577385</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7256263</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126519297</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91541</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>658</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>576860</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7256098</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126517692</v>
+      </c>
+      <c r="B16" t="n">
+        <v>82792</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>577229</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7255956</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126516443</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91263</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>577448</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7256136</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126516465</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91263</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>577402</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7256168</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126518858</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91241</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>576624</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7256239</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126515991</v>
+      </c>
+      <c r="B20" t="n">
+        <v>75075</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>577501</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7256044</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126518137</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79059</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>864</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>576958</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7255988</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126519313</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91263</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>576860</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7256098</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126519060</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91259</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>576475</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7256157</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126516763</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91263</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>577407</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7256296</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126517198</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91263</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>577286</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7256040</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126518162</v>
+      </c>
+      <c r="B26" t="n">
+        <v>82792</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>576958</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7255988</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126515920</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91259</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>577467</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7256029</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126518993</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91699</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>576538</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7256170</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126518228</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91947</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>67</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>576959</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7256037</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58922-2024 artfynd.xlsx
+++ b/artfynd/A 58922-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2595,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126515991</v>
+        <v>126518137</v>
       </c>
       <c r="B20" t="n">
-        <v>75075</v>
+        <v>79059</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,21 +2606,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577501</v>
+        <v>576958</v>
       </c>
       <c r="R20" t="n">
-        <v>7256044</v>
+        <v>7255988</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2697,10 +2697,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126518137</v>
+        <v>126515991</v>
       </c>
       <c r="B21" t="n">
-        <v>79059</v>
+        <v>75075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2708,21 +2708,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576958</v>
+        <v>577501</v>
       </c>
       <c r="R21" t="n">
-        <v>7255988</v>
+        <v>7256044</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3207,32 +3207,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126518162</v>
+        <v>126518993</v>
       </c>
       <c r="B26" t="n">
-        <v>82792</v>
+        <v>91699</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576958</v>
+        <v>576538</v>
       </c>
       <c r="R26" t="n">
-        <v>7255988</v>
+        <v>7256170</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3309,10 +3309,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126515920</v>
+        <v>126518162</v>
       </c>
       <c r="B27" t="n">
-        <v>91259</v>
+        <v>82792</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3320,21 +3320,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577467</v>
+        <v>576958</v>
       </c>
       <c r="R27" t="n">
-        <v>7256029</v>
+        <v>7255988</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,32 +3411,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126518993</v>
+        <v>126515920</v>
       </c>
       <c r="B28" t="n">
-        <v>91699</v>
+        <v>91259</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576538</v>
+        <v>577467</v>
       </c>
       <c r="R28" t="n">
-        <v>7256170</v>
+        <v>7256029</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3613,6 +3613,1666 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126532747</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91819</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>760</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>575547</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7255854</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126532844</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80084</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>575504</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7255841</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126542717</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91259</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>575393</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7256043</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126532587</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80084</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>575667</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7255885</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126532429</v>
+      </c>
+      <c r="B34" t="n">
+        <v>77944</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>314</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vitskaftad svartspik</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis viridialba</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>575845</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7256028</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126532521</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92180</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>575768</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7255994</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126542758</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91241</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>575257</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7255911</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126542723</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91699</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>575393</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7256043</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126532435</v>
+      </c>
+      <c r="B38" t="n">
+        <v>75075</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>575845</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7256028</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126542751</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91614</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>575257</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7255911</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126542720</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91541</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>658</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>575393</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7256043</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126542766</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91241</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>575139</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7255775</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126532372</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91263</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>575827</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7256031</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126542755</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91245</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>575257</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7255911</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126532249</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91259</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>575775</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7255741</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126534921</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91241</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Akkakalven, Akkakalven, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>574625</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7255682</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58922-2024 artfynd.xlsx
+++ b/artfynd/A 58922-2024 artfynd.xlsx
@@ -3819,10 +3819,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126542717</v>
+        <v>126532587</v>
       </c>
       <c r="B32" t="n">
-        <v>91259</v>
+        <v>80084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3830,37 +3830,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575393</v>
+        <v>575667</v>
       </c>
       <c r="R32" t="n">
-        <v>7256043</v>
+        <v>7255885</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3901,7 +3898,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3925,10 +3921,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126532587</v>
+        <v>126542717</v>
       </c>
       <c r="B33" t="n">
-        <v>80084</v>
+        <v>91259</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3936,34 +3932,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575667</v>
+        <v>575393</v>
       </c>
       <c r="R33" t="n">
-        <v>7255885</v>
+        <v>7256043</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4004,6 +4003,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58922-2024 artfynd.xlsx
+++ b/artfynd/A 58922-2024 artfynd.xlsx
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126518951</v>
+        <v>126517759</v>
       </c>
       <c r="B8" t="n">
-        <v>80084</v>
+        <v>75080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,21 +1382,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576556</v>
+        <v>577186</v>
       </c>
       <c r="R8" t="n">
-        <v>7256164</v>
+        <v>7255953</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126517759</v>
+        <v>126518951</v>
       </c>
       <c r="B9" t="n">
-        <v>75080</v>
+        <v>80084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,21 +1484,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577186</v>
+        <v>576556</v>
       </c>
       <c r="R9" t="n">
-        <v>7255953</v>
+        <v>7256164</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -3615,32 +3615,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126532747</v>
+        <v>126532844</v>
       </c>
       <c r="B30" t="n">
-        <v>91819</v>
+        <v>80084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575547</v>
+        <v>575504</v>
       </c>
       <c r="R30" t="n">
-        <v>7255854</v>
+        <v>7255841</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3717,32 +3717,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126532844</v>
+        <v>126532747</v>
       </c>
       <c r="B31" t="n">
-        <v>80084</v>
+        <v>91819</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575504</v>
+        <v>575547</v>
       </c>
       <c r="R31" t="n">
-        <v>7255841</v>
+        <v>7255854</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3819,10 +3819,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126532587</v>
+        <v>126542717</v>
       </c>
       <c r="B32" t="n">
-        <v>80084</v>
+        <v>91259</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3830,34 +3830,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575667</v>
+        <v>575393</v>
       </c>
       <c r="R32" t="n">
-        <v>7255885</v>
+        <v>7256043</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3898,6 +3901,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3921,10 +3925,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126542717</v>
+        <v>126532587</v>
       </c>
       <c r="B33" t="n">
-        <v>91259</v>
+        <v>80084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3932,37 +3936,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575393</v>
+        <v>575667</v>
       </c>
       <c r="R33" t="n">
-        <v>7256043</v>
+        <v>7255885</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4003,7 +4004,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58922-2024 artfynd.xlsx
+++ b/artfynd/A 58922-2024 artfynd.xlsx
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126517759</v>
+        <v>126518951</v>
       </c>
       <c r="B8" t="n">
-        <v>75080</v>
+        <v>80084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,21 +1382,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577186</v>
+        <v>576556</v>
       </c>
       <c r="R8" t="n">
-        <v>7255953</v>
+        <v>7256164</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126518951</v>
+        <v>126517759</v>
       </c>
       <c r="B9" t="n">
-        <v>80084</v>
+        <v>75080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,21 +1484,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576556</v>
+        <v>577186</v>
       </c>
       <c r="R9" t="n">
-        <v>7256164</v>
+        <v>7255953</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -3615,32 +3615,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126532844</v>
+        <v>126532747</v>
       </c>
       <c r="B30" t="n">
-        <v>80084</v>
+        <v>91819</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575504</v>
+        <v>575547</v>
       </c>
       <c r="R30" t="n">
-        <v>7255841</v>
+        <v>7255854</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3717,32 +3717,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126532747</v>
+        <v>126532844</v>
       </c>
       <c r="B31" t="n">
-        <v>91819</v>
+        <v>80084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575547</v>
+        <v>575504</v>
       </c>
       <c r="R31" t="n">
-        <v>7255854</v>
+        <v>7255841</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3819,10 +3819,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126542717</v>
+        <v>126532587</v>
       </c>
       <c r="B32" t="n">
-        <v>91259</v>
+        <v>80084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3830,37 +3830,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575393</v>
+        <v>575667</v>
       </c>
       <c r="R32" t="n">
-        <v>7256043</v>
+        <v>7255885</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3901,7 +3898,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3925,10 +3921,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126532587</v>
+        <v>126542717</v>
       </c>
       <c r="B33" t="n">
-        <v>80084</v>
+        <v>91259</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3936,34 +3932,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575667</v>
+        <v>575393</v>
       </c>
       <c r="R33" t="n">
-        <v>7255885</v>
+        <v>7256043</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4004,6 +4003,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58922-2024 artfynd.xlsx
+++ b/artfynd/A 58922-2024 artfynd.xlsx
@@ -3615,32 +3615,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126532844</v>
+        <v>126532747</v>
       </c>
       <c r="B30" t="n">
-        <v>80084</v>
+        <v>91893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575504</v>
+        <v>575547</v>
       </c>
       <c r="R30" t="n">
-        <v>7255841</v>
+        <v>7255854</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3717,32 +3717,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126532747</v>
+        <v>126532844</v>
       </c>
       <c r="B31" t="n">
-        <v>91819</v>
+        <v>80115</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575547</v>
+        <v>575504</v>
       </c>
       <c r="R31" t="n">
-        <v>7255854</v>
+        <v>7255841</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,7 +3822,7 @@
         <v>126532587</v>
       </c>
       <c r="B32" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>126542717</v>
       </c>
       <c r="B33" t="n">
-        <v>91259</v>
+        <v>91333</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4027,32 +4027,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126532521</v>
+        <v>126532429</v>
       </c>
       <c r="B34" t="n">
-        <v>92180</v>
+        <v>78004</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4062,10 +4062,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575768</v>
+        <v>575845</v>
       </c>
       <c r="R34" t="n">
-        <v>7255994</v>
+        <v>7256028</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4129,32 +4129,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126532429</v>
+        <v>126532521</v>
       </c>
       <c r="B35" t="n">
-        <v>77944</v>
+        <v>92254</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>314</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575845</v>
+        <v>575768</v>
       </c>
       <c r="R35" t="n">
-        <v>7256028</v>
+        <v>7255994</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4234,7 +4234,7 @@
         <v>126542758</v>
       </c>
       <c r="B36" t="n">
-        <v>91241</v>
+        <v>91315</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4337,45 +4337,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126532435</v>
+        <v>126542723</v>
       </c>
       <c r="B37" t="n">
-        <v>75075</v>
+        <v>91773</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575845</v>
+        <v>575393</v>
       </c>
       <c r="R37" t="n">
-        <v>7256028</v>
+        <v>7256043</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4416,6 +4419,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4439,48 +4443,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126542723</v>
+        <v>126532435</v>
       </c>
       <c r="B38" t="n">
-        <v>91699</v>
+        <v>75135</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575393</v>
+        <v>575845</v>
       </c>
       <c r="R38" t="n">
-        <v>7256043</v>
+        <v>7256028</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4521,7 +4522,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>126542751</v>
       </c>
       <c r="B39" t="n">
-        <v>91614</v>
+        <v>91688</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>126542720</v>
       </c>
       <c r="B40" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>126542766</v>
       </c>
       <c r="B41" t="n">
-        <v>91241</v>
+        <v>91315</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>126532372</v>
       </c>
       <c r="B42" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>126542755</v>
       </c>
       <c r="B43" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>126532249</v>
       </c>
       <c r="B44" t="n">
-        <v>91259</v>
+        <v>91333</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>126534921</v>
       </c>
       <c r="B45" t="n">
-        <v>91241</v>
+        <v>91315</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 58922-2024 artfynd.xlsx
+++ b/artfynd/A 58922-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88055852</v>
+        <v>126518228</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stormyran, Storuman, Ly lm</t>
+          <t>Stormyran, Stormyran, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576229.1735632694</v>
+        <v>576959</v>
       </c>
       <c r="R2" t="n">
-        <v>7256158.144015239</v>
+        <v>7256037</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,35 +756,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl Jansson, Åsa Stenman, Henrik Sporrong</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88055843</v>
+        <v>126516972</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stormyran, Storuman, Ly lm</t>
+          <t>Stormyran, Stormyran, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576520.9852405002</v>
+        <v>577321</v>
       </c>
       <c r="R3" t="n">
-        <v>7256244.930768974</v>
+        <v>7256133</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,73 +858,69 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson, Åsa Stenman, Henrik Sporrong</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88055839</v>
+        <v>126532429</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stormyran, Storuman, Ly lm</t>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576457.0936553847</v>
+        <v>575845</v>
       </c>
       <c r="R4" t="n">
-        <v>7256104.097239666</v>
+        <v>7256028</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,35 +960,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson, Åsa Stenman, Henrik Sporrong</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88055840</v>
+        <v>88055839</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576465.9627178158</v>
+        <v>576457</v>
       </c>
       <c r="R5" t="n">
-        <v>7256131.828767239</v>
+        <v>7256104</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1049,9 @@
           <t>2020-09-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,53 +1082,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88055842</v>
+        <v>126519297</v>
       </c>
       <c r="B6" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stormyran, Storuman, Ly lm</t>
+          <t>Stormyran, Stormyran, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576533.005977735</v>
+        <v>576860</v>
       </c>
       <c r="R6" t="n">
-        <v>7256168.16555629</v>
+        <v>7256098</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,22 +1147,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,35 +1163,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson, Åsa Stenman, Henrik Sporrong</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88055841</v>
+        <v>126542720</v>
       </c>
       <c r="B7" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,37 +1195,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stormyran, Storuman, Ly lm</t>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576533.7960840475</v>
+        <v>575393</v>
       </c>
       <c r="R7" t="n">
-        <v>7256169.85285438</v>
+        <v>7256043</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,22 +1252,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,67 +1266,69 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carl Jansson, Åsa Stenman, Henrik Sporrong</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126518951</v>
+        <v>126532747</v>
       </c>
       <c r="B8" t="n">
-        <v>80084</v>
+        <v>92509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ly lm</t>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576556</v>
+        <v>575547</v>
       </c>
       <c r="R8" t="n">
-        <v>7256164</v>
+        <v>7255854</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,12 +1355,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126517759</v>
+        <v>126518137</v>
       </c>
       <c r="B9" t="n">
-        <v>75080</v>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,21 +1403,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577186</v>
+        <v>576958</v>
       </c>
       <c r="R9" t="n">
-        <v>7255953</v>
+        <v>7255988</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126516972</v>
+        <v>88055841</v>
       </c>
       <c r="B10" t="n">
-        <v>75067</v>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,37 +1505,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ly lm</t>
+          <t>Stormyran, Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577321</v>
+        <v>576534</v>
       </c>
       <c r="R10" t="n">
-        <v>7256133</v>
+        <v>7256170</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,12 +1559,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,31 +1575,30 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Luckig, lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Carl Jansson, Åsa Stenman, Henrik Sporrong</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126517699</v>
+        <v>126516771</v>
       </c>
       <c r="B11" t="n">
-        <v>91263</v>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,21 +1606,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1712,10 +1630,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577229</v>
+        <v>577385</v>
       </c>
       <c r="R11" t="n">
-        <v>7255956</v>
+        <v>7256263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,10 +1697,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126518234</v>
+        <v>126518858</v>
       </c>
       <c r="B12" t="n">
-        <v>91245</v>
+        <v>91905</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,21 +1708,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1814,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576959</v>
+        <v>576624</v>
       </c>
       <c r="R12" t="n">
-        <v>7256037</v>
+        <v>7256239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1881,10 +1799,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126515967</v>
+        <v>126542758</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>91905</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,34 +1810,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ly lm</t>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577501</v>
+        <v>575257</v>
       </c>
       <c r="R13" t="n">
-        <v>7256044</v>
+        <v>7255911</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,12 +1867,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1960,6 +1881,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1983,10 +1905,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126516771</v>
+        <v>126542766</v>
       </c>
       <c r="B14" t="n">
-        <v>91241</v>
+        <v>91905</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2012,16 +1934,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ly lm</t>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577385</v>
+        <v>575139</v>
       </c>
       <c r="R14" t="n">
-        <v>7256263</v>
+        <v>7255775</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,12 +1973,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2062,6 +1987,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2085,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126519297</v>
+        <v>88055840</v>
       </c>
       <c r="B15" t="n">
-        <v>91541</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,37 +2022,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ly lm</t>
+          <t>Stormyran, Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576860</v>
+        <v>576466</v>
       </c>
       <c r="R15" t="n">
-        <v>7256098</v>
+        <v>7256132</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2150,12 +2076,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2166,31 +2092,30 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Luckig, lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Carl Jansson, Åsa Stenman, Henrik Sporrong</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126517692</v>
+        <v>126518234</v>
       </c>
       <c r="B16" t="n">
-        <v>82792</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,21 +2123,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2222,10 +2147,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577229</v>
+        <v>576959</v>
       </c>
       <c r="R16" t="n">
-        <v>7255956</v>
+        <v>7256037</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126516443</v>
+        <v>126542755</v>
       </c>
       <c r="B17" t="n">
-        <v>91263</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,34 +2225,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ly lm</t>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577448</v>
+        <v>575257</v>
       </c>
       <c r="R17" t="n">
-        <v>7256136</v>
+        <v>7255911</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,12 +2282,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2368,6 +2296,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2391,48 +2320,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126516465</v>
+        <v>88055852</v>
       </c>
       <c r="B18" t="n">
-        <v>91263</v>
+        <v>91923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ly lm</t>
+          <t>Stormyran, Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577402</v>
+        <v>576229</v>
       </c>
       <c r="R18" t="n">
-        <v>7256168</v>
+        <v>7256158</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2456,12 +2385,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2472,53 +2401,52 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Luckig, lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Carl Jansson, Åsa Stenman, Henrik Sporrong</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126518858</v>
+        <v>126515920</v>
       </c>
       <c r="B19" t="n">
-        <v>91241</v>
+        <v>91923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2528,10 +2456,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576624</v>
+        <v>577467</v>
       </c>
       <c r="R19" t="n">
-        <v>7256239</v>
+        <v>7256029</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,32 +2523,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126518137</v>
+        <v>126519060</v>
       </c>
       <c r="B20" t="n">
-        <v>79059</v>
+        <v>91923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2630,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576958</v>
+        <v>576475</v>
       </c>
       <c r="R20" t="n">
-        <v>7255988</v>
+        <v>7256157</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2697,45 +2625,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126515991</v>
+        <v>126532249</v>
       </c>
       <c r="B21" t="n">
-        <v>75075</v>
+        <v>91923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ly lm</t>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577501</v>
+        <v>575775</v>
       </c>
       <c r="R21" t="n">
-        <v>7256044</v>
+        <v>7255741</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,12 +2690,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2799,45 +2727,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126519313</v>
+        <v>126542717</v>
       </c>
       <c r="B22" t="n">
-        <v>91263</v>
+        <v>91923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ly lm</t>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576860</v>
+        <v>575393</v>
       </c>
       <c r="R22" t="n">
-        <v>7256098</v>
+        <v>7256043</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2864,12 +2795,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2878,6 +2809,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2901,10 +2833,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126519060</v>
+        <v>88055842</v>
       </c>
       <c r="B23" t="n">
-        <v>91259</v>
+        <v>92369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2912,37 +2844,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ly lm</t>
+          <t>Stormyran, Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576475</v>
+        <v>576533</v>
       </c>
       <c r="R23" t="n">
-        <v>7256157</v>
+        <v>7256168</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2966,12 +2898,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2982,31 +2914,30 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Luckig, lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Carl Jansson, Åsa Stenman, Henrik Sporrong</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126517198</v>
+        <v>126518993</v>
       </c>
       <c r="B24" t="n">
-        <v>91263</v>
+        <v>92369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3038,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577286</v>
+        <v>576538</v>
       </c>
       <c r="R24" t="n">
-        <v>7256040</v>
+        <v>7256170</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3105,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126516763</v>
+        <v>126542723</v>
       </c>
       <c r="B25" t="n">
-        <v>91263</v>
+        <v>92369</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3116,34 +3047,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ly lm</t>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577407</v>
+        <v>575393</v>
       </c>
       <c r="R25" t="n">
-        <v>7256296</v>
+        <v>7256043</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3170,12 +3104,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3184,6 +3118,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3207,10 +3142,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126515920</v>
+        <v>126517692</v>
       </c>
       <c r="B26" t="n">
-        <v>91259</v>
+        <v>83173</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3218,21 +3153,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3242,10 +3177,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577467</v>
+        <v>577229</v>
       </c>
       <c r="R26" t="n">
-        <v>7256029</v>
+        <v>7255956</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3312,7 +3247,7 @@
         <v>126518162</v>
       </c>
       <c r="B27" t="n">
-        <v>82792</v>
+        <v>83173</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3411,32 +3346,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126518993</v>
+        <v>126517759</v>
       </c>
       <c r="B28" t="n">
-        <v>91699</v>
+        <v>83312</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>1467</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3446,10 +3381,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576538</v>
+        <v>577186</v>
       </c>
       <c r="R28" t="n">
-        <v>7256170</v>
+        <v>7255953</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3513,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126518228</v>
+        <v>126542751</v>
       </c>
       <c r="B29" t="n">
-        <v>91947</v>
+        <v>92292</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3524,34 +3459,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>67</v>
+        <v>1506</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ly lm</t>
+          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576959</v>
+        <v>575257</v>
       </c>
       <c r="R29" t="n">
-        <v>7256037</v>
+        <v>7255911</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3578,12 +3516,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3592,6 +3530,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3615,45 +3554,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126532747</v>
+        <v>126518951</v>
       </c>
       <c r="B30" t="n">
-        <v>91893</v>
+        <v>80433</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+          <t>Stormyran, Stormyran, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575547</v>
+        <v>576556</v>
       </c>
       <c r="R30" t="n">
-        <v>7255854</v>
+        <v>7256164</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,12 +3619,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3717,10 +3656,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126532844</v>
+        <v>126532587</v>
       </c>
       <c r="B31" t="n">
-        <v>80115</v>
+        <v>80433</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575504</v>
+        <v>575667</v>
       </c>
       <c r="R31" t="n">
-        <v>7255841</v>
+        <v>7255885</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3819,10 +3758,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126532587</v>
+        <v>126532844</v>
       </c>
       <c r="B32" t="n">
-        <v>80115</v>
+        <v>80433</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,10 +3793,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575667</v>
+        <v>575504</v>
       </c>
       <c r="R32" t="n">
-        <v>7255885</v>
+        <v>7255841</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3921,48 +3860,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126542717</v>
+        <v>126532521</v>
       </c>
       <c r="B33" t="n">
-        <v>91333</v>
+        <v>92869</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575393</v>
+        <v>575768</v>
       </c>
       <c r="R33" t="n">
-        <v>7256043</v>
+        <v>7255994</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4003,7 +3939,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4027,45 +3962,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126532429</v>
+        <v>126515967</v>
       </c>
       <c r="B34" t="n">
-        <v>78004</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+          <t>Stormyran, Stormyran, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575845</v>
+        <v>577501</v>
       </c>
       <c r="R34" t="n">
-        <v>7256028</v>
+        <v>7256044</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4092,12 +4027,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4129,45 +4064,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126532521</v>
+        <v>126515991</v>
       </c>
       <c r="B35" t="n">
-        <v>92254</v>
+        <v>83307</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+          <t>Stormyran, Stormyran, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575768</v>
+        <v>577501</v>
       </c>
       <c r="R35" t="n">
-        <v>7255994</v>
+        <v>7256044</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4194,12 +4129,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4231,10 +4166,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126542758</v>
+        <v>126532435</v>
       </c>
       <c r="B36" t="n">
-        <v>91315</v>
+        <v>83307</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4242,37 +4177,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575257</v>
+        <v>575845</v>
       </c>
       <c r="R36" t="n">
-        <v>7255911</v>
+        <v>7256028</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4313,7 +4245,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4337,48 +4268,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126542723</v>
+        <v>126534921</v>
       </c>
       <c r="B37" t="n">
-        <v>91773</v>
+        <v>91905</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
+          <t>Akkakalven, Akkakalven, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575393</v>
+        <v>574625</v>
       </c>
       <c r="R37" t="n">
-        <v>7256043</v>
+        <v>7255682</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4419,7 +4347,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4440,838 +4367,6 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>126532435</v>
-      </c>
-      <c r="B38" t="n">
-        <v>75135</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>575845</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7256028</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Luckig, lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>126542751</v>
-      </c>
-      <c r="B39" t="n">
-        <v>91688</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>1506</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Ostticka</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Skeletocutis odora</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>575257</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7255911</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Luckig, lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>126542720</v>
-      </c>
-      <c r="B40" t="n">
-        <v>91615</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>658</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>575393</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7256043</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Luckig, lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>126542766</v>
-      </c>
-      <c r="B41" t="n">
-        <v>91315</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>575139</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7255775</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Luckig, lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>126532372</v>
-      </c>
-      <c r="B42" t="n">
-        <v>91337</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>575827</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7256031</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Luckig, lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>126542755</v>
-      </c>
-      <c r="B43" t="n">
-        <v>91319</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>575257</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7255911</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Luckig, lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>126532249</v>
-      </c>
-      <c r="B44" t="n">
-        <v>91333</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Dammtjärnen, Dammtjärnen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>575775</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7255741</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Luckig, lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>126534921</v>
-      </c>
-      <c r="B45" t="n">
-        <v>91315</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Akkakalven, Akkakalven, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>574625</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7255682</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Luckig, lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
